--- a/output/10_集計結果.xlsx
+++ b/output/10_集計結果.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="目次" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ニーズ単純集計" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ニーズ軸別集計" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="在宅単純集計" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="在宅軸別集計" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分析クロス" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="派生変数" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設問一覧" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="目次" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ニーズ単純集計" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ニーズ軸別集計" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="在宅単純集計" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="在宅軸別集計" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="分析クロス" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="派生変数" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="設問一覧" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -491,14 +491,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第10期北塩原村 アンケート調査　集計結果</t>
+          <t>第10期北塩原村 アンケート調査　集計結果（ダミーデータによる検証用）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>集計仕様書（doc25）に基づく。設問の定義はコードブック（data/集計_コードブック.json）による。</t>
+          <t>★★ これはダミーデータによる検証用です。実際の回答ではありません ★★　集計仕様書（doc25）に基づく。設問の定義はコードブック（data/集計_コードブック.json）による。　調査票の回収後、本番のデータで作り直します。</t>
         </is>
       </c>
     </row>
@@ -82188,7 +82188,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>第1層＝R99が0かつP01該当／第2層＝R99が0かつP01非該当／第3層＝R99が1以上かつ認定なし／第4層＝認定あり</t>
+          <t>第1層＝R99が0かつP01該当／第2層＝R99が0かつP01非該当／第3層＝R99が1以上かつ認定なし（事業対象者を含む）／第4層＝認定あり</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -82294,12 +82294,12 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>認定データ</t>
+          <t>認定データ・総合事業の対象者情報</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>認定なし／要支援1・2／要介護1・2／要介護3〜5</t>
+          <t>認定なし／事業対象者／要支援1・2／要介護1以上（4区分）。ニーズ調査の対象は一般高齢者・事業対象者・要支援認定者のため要介護1以上は少数</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
